--- a/04_Problem4_Delinquency_Escalation_Loss_Severity/reports/financial_impact_reporting_packaging/AMEX_Problem4_Financial_Impact_Workbook.xlsx
+++ b/04_Problem4_Delinquency_Escalation_Loss_Severity/reports/financial_impact_reporting_packaging/AMEX_Problem4_Financial_Impact_Workbook.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +81,9 @@
       <color rgb="000B1F3A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -127,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +168,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -717,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A2:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -727,7 +731,6 @@
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -833,6 +836,30 @@
       <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Rows 5-7 and 9 recalculate live from the Assumptions and Tier Financial Detail sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Business Impact — Modeled Estimate, Not Audited Value</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The $19,435,432 change in recognized loss and the $9,690,840 estimated loss prevented per scoring cycle are self-computed under this report's own tiering and 15% ASSUMPTION-based intervention-success rate -- they have not been audited by a third party or realized inside a live institution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Independent Audit Status</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>This project was developed as an independent portfolio body of work and has not undergone formal validation, audit, or sign-off by a financial institution's model risk management (SR 11-7 or equivalent) function, a third-party auditor, or a regulator. All model outputs, risk metrics, and business-impact figures in this report are self-computed under the assumptions stated herein and have not been realized in a live production environment at a financial institution.</t>
         </is>
       </c>
     </row>
